--- a/data/out/test1/001328648_Python版_2pt.xlsx
+++ b/data/out/test1/001328648_Python版_2pt.xlsx
@@ -19,13 +19,37 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="13.14"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="10.9"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="9.800000000000001"/>
+    </font>
+    <font>
+      <name val="MS Gothic"/>
+      <sz val="6.5"/>
     </font>
     <font>
       <name val="MS Gothic"/>
@@ -142,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,46 +179,100 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +722,7 @@
     </row>
     <row r="5">
       <c r="B5" s="7"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>※太枠の中に書いてください。</t>
         </is>
@@ -653,27 +731,27 @@
     </row>
     <row r="6">
       <c r="B6" s="7"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>（地方）法務局</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>支局・出張所</t>
         </is>
       </c>
-      <c r="W6" s="8" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="Z6" s="8" t="inlineStr">
+      <c r="Z6" s="11" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AC6" s="8" t="inlineStr">
+      <c r="AC6" s="11" t="inlineStr">
         <is>
           <t>日届出</t>
         </is>
@@ -684,7 +762,7 @@
       <c r="B7" s="7"/>
       <c r="C7" s="4"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
@@ -694,7 +772,7 @@
       <c r="H7" s="5"/>
       <c r="I7" s="6"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
@@ -724,18 +802,18 @@
     </row>
     <row r="8">
       <c r="B8" s="7"/>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
       <c r="I8" s="9"/>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="15" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
@@ -762,19 +840,19 @@
     </row>
     <row r="9">
       <c r="B9" s="7"/>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー廃止届出</t>
         </is>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="1"/>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
@@ -782,45 +860,45 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="14"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="15"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="18"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="18"/>
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
+      <c r="AD9" s="18"/>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="19"/>
       <c r="AH9" s="9"/>
     </row>
     <row r="10">
       <c r="B10" s="7"/>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>廃止届出</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
       <c r="I10" s="9"/>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
@@ -846,18 +924,18 @@
     </row>
     <row r="11">
       <c r="B11" s="7"/>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印をつけてください。)</t>
         </is>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>印資格(</t>
         </is>
@@ -866,28 +944,28 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="19" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
       </c>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="20" t="inlineStr">
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="18"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="18"/>
+      <c r="AF11" s="25" t="inlineStr">
         <is>
           <t>)</t>
         </is>
@@ -896,23 +974,23 @@
     </row>
     <row r="12">
       <c r="B12" s="7"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
       <c r="I12" s="9"/>
-      <c r="J12" s="21" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>鑑氏名</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>資 格</t>
         </is>
       </c>
-      <c r="O12" s="17" t="inlineStr">
+      <c r="O12" s="27" t="inlineStr">
         <is>
           <t>( )</t>
         </is>
@@ -938,18 +1016,18 @@
     </row>
     <row r="13">
       <c r="B13" s="7"/>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印を</t>
         </is>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="J13" s="26" t="inlineStr">
         <is>
           <t>提</t>
         </is>
       </c>
-      <c r="K13" s="22" t="inlineStr">
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
@@ -957,44 +1035,44 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="15"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="18"/>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="18"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="18"/>
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
+      <c r="AD13" s="18"/>
+      <c r="AE13" s="18"/>
+      <c r="AF13" s="19"/>
       <c r="AH13" s="9"/>
     </row>
     <row r="14">
       <c r="B14" s="7"/>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>つけてください。)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="29" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="24" t="inlineStr">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="30" t="inlineStr">
         <is>
           <t>出</t>
         </is>
@@ -1013,20 +1091,20 @@
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
-      <c r="Y14" s="10" t="inlineStr">
+      <c r="Y14" s="31" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
       <c r="Z14" s="5"/>
       <c r="AA14" s="5"/>
-      <c r="AB14" s="10" t="inlineStr">
+      <c r="AB14" s="31" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
       <c r="AC14" s="5"/>
-      <c r="AD14" s="10" t="inlineStr">
+      <c r="AD14" s="31" t="inlineStr">
         <is>
           <t>日生</t>
         </is>
@@ -1037,12 +1115,12 @@
     </row>
     <row r="15">
       <c r="B15" s="7"/>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>登記所に提出した</t>
         </is>
@@ -1052,60 +1130,60 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="6"/>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="K15" s="19" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t>大・昭・平・西暦 年 月 日生</t>
         </is>
       </c>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-      <c r="AF15" s="15"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="18"/>
+      <c r="Y15" s="18"/>
+      <c r="Z15" s="18"/>
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="18"/>
+      <c r="AE15" s="18"/>
+      <c r="AF15" s="19"/>
       <c r="AH15" s="9"/>
     </row>
     <row r="16">
       <c r="B16" s="7"/>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>登 記 所 に 提 出 し た</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="33" t="inlineStr">
         <is>
           <t>印鑑の押印欄印鑑カード番号</t>
         </is>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
       <c r="J16" s="4"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -1133,7 +1211,7 @@
     </row>
     <row r="17">
       <c r="B17" s="7"/>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>印 鑑 の 押 印 欄</t>
         </is>
@@ -1144,52 +1222,52 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="6"/>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>印鑑カード番号</t>
         </is>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="23" t="inlineStr">
+      <c r="K17" s="18"/>
+      <c r="L17" s="34" t="inlineStr">
         <is>
           <t>カード廃止の理由</t>
         </is>
       </c>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="23" t="inlineStr">
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="18"/>
+      <c r="T17" s="29" t="inlineStr">
         <is>
           <t>亡失（なくなった）</t>
         </is>
       </c>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="23" t="inlineStr">
+      <c r="U17" s="18"/>
+      <c r="V17" s="18"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="18"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="29" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="15"/>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="18"/>
+      <c r="AE17" s="18"/>
+      <c r="AF17" s="19"/>
       <c r="AH17" s="9"/>
     </row>
     <row r="18">
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="J18" s="35" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、</t>
         </is>
@@ -1203,7 +1281,7 @@
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
-      <c r="T18" s="10" t="inlineStr">
+      <c r="T18" s="12" t="inlineStr">
         <is>
           <t>汚損（著しく汚れた)</t>
         </is>
@@ -1226,17 +1304,17 @@
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、 汚損（著しく汚れた)</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K19" s="36" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="T19" s="10" t="inlineStr">
         <is>
           <t>き損（破損した）</t>
         </is>
@@ -1248,58 +1326,58 @@
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="I20" s="9"/>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="24" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。 き損（破損した）</t>
         </is>
       </c>
-      <c r="K20" s="23" t="inlineStr">
+      <c r="K20" s="34" t="inlineStr">
         <is>
           <t>申請人（注２）</t>
         </is>
       </c>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="23" t="inlineStr">
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="34" t="inlineStr">
         <is>
           <t>印鑑提出者本人代理人</t>
         </is>
       </c>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="15"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="18"/>
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
+      <c r="AD20" s="18"/>
+      <c r="AE20" s="18"/>
+      <c r="AF20" s="19"/>
       <c r="AH20" s="9"/>
     </row>
     <row r="21">
       <c r="B21" s="7"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="22" t="inlineStr">
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>申 請 人（注２） 印鑑提出者本人 代理人</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
@@ -1330,7 +1408,7 @@
     <row r="22">
       <c r="B22" s="7"/>
       <c r="C22" s="4"/>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="32" t="inlineStr">
         <is>
           <t>（印鑑は鮮明に押</t>
         </is>
@@ -1340,12 +1418,12 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="6"/>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J22" s="15" t="inlineStr">
         <is>
           <t>住 所</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K22" s="37" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
@@ -1354,22 +1432,22 @@
     </row>
     <row r="23">
       <c r="B23" s="7"/>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>（ 印 鑑 は 鮮 明 に 押</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="33" t="inlineStr">
         <is>
           <t>印してください。）氏名</t>
         </is>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="22" t="inlineStr">
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
@@ -1400,7 +1478,7 @@
     </row>
     <row r="24">
       <c r="B24" s="7"/>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>印 し て く だ さ い 。 ）</t>
         </is>
@@ -1411,7 +1489,7 @@
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="38" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
@@ -1442,22 +1520,22 @@
     </row>
     <row r="25">
       <c r="B25" s="7"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>委 任 状</t>
         </is>
       </c>
-      <c r="P25" s="8" t="inlineStr">
+      <c r="P25" s="10" t="inlineStr">
         <is>
           <t>委</t>
         </is>
       </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
+      <c r="V25" s="10" t="inlineStr">
         <is>
           <t>状</t>
         </is>
@@ -1467,13 +1545,13 @@
     </row>
     <row r="26">
       <c r="B26" s="7"/>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="39" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
@@ -1486,17 +1564,17 @@
     </row>
     <row r="27">
       <c r="B27" s="7"/>
-      <c r="C27" s="12" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="40" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
@@ -1508,17 +1586,17 @@
     </row>
     <row r="28">
       <c r="B28" s="7"/>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>を代理人と定め、 印鑑の廃止届出、 印鑑カードの廃止届出、 印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>を代理人と定め、の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
@@ -1528,22 +1606,22 @@
     </row>
     <row r="29">
       <c r="B29" s="7"/>
-      <c r="C29" s="12" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>の廃止届出、 添付書面の原本還付請求及び受領の権限を委任します。</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="10" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>日</t>
         </is>
@@ -1553,12 +1631,12 @@
     </row>
     <row r="30">
       <c r="B30" s="7"/>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>年 月 日</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
@@ -1568,17 +1646,17 @@
     </row>
     <row r="31">
       <c r="B31" s="7"/>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>住 所</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="AB31" s="8" t="inlineStr">
+      <c r="AB31" s="22" t="inlineStr">
         <is>
           <t>登記所に提</t>
         </is>
@@ -1588,17 +1666,17 @@
     </row>
     <row r="32">
       <c r="B32" s="7"/>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>登 記 所 に 提</t>
         </is>
       </c>
-      <c r="Y32" s="8" t="inlineStr">
+      <c r="Y32" s="10" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AB32" s="8" t="inlineStr">
+      <c r="AB32" s="22" t="inlineStr">
         <is>
           <t>出した印鑑</t>
         </is>
@@ -1608,17 +1686,17 @@
     </row>
     <row r="33">
       <c r="B33" s="7"/>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>氏 名</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>（注１）登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
@@ -1628,12 +1706,12 @@
     </row>
     <row r="34">
       <c r="B34" s="7"/>
-      <c r="C34" s="12" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
@@ -1643,12 +1721,12 @@
     </row>
     <row r="35">
       <c r="B35" s="7"/>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>出 し た 印 鑑</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）は、□にレ印をつけてください。</t>
         </is>
@@ -1658,12 +1736,12 @@
     </row>
     <row r="36">
       <c r="B36" s="7"/>
-      <c r="C36" s="12" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="22" t="inlineStr">
         <is>
           <t>（注２）事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
@@ -1673,12 +1751,12 @@
     </row>
     <row r="37">
       <c r="B37" s="7"/>
-      <c r="C37" s="12" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>（注１） 登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G37" s="22" t="inlineStr">
         <is>
           <t>この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
         </is>
@@ -1688,22 +1766,22 @@
     </row>
     <row r="38">
       <c r="B38" s="7"/>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>（注３）村長の証明した印鑑証明書を添付してください。印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
       </c>
-      <c r="Q38" s="25"/>
+      <c r="Q38" s="41"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
       <c r="U38" s="3"/>
-      <c r="V38" s="25"/>
+      <c r="V38" s="41"/>
       <c r="W38" s="1"/>
       <c r="X38" s="3"/>
       <c r="Y38" s="1"/>
@@ -1718,17 +1796,17 @@
     </row>
     <row r="39">
       <c r="B39" s="7"/>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="22" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合</t>
         </is>
       </c>
-      <c r="Q39" s="17" t="inlineStr">
+      <c r="Q39" s="27" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
@@ -1738,27 +1816,27 @@
       <c r="T39" s="5"/>
       <c r="U39" s="5"/>
       <c r="V39" s="6"/>
-      <c r="W39" s="17" t="inlineStr">
+      <c r="W39" s="27" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
       </c>
       <c r="X39" s="6"/>
-      <c r="Y39" s="17" t="inlineStr">
+      <c r="Y39" s="27" t="inlineStr">
         <is>
           <t>調 査</t>
         </is>
       </c>
       <c r="Z39" s="5"/>
       <c r="AA39" s="6"/>
-      <c r="AB39" s="17" t="inlineStr">
+      <c r="AB39" s="27" t="inlineStr">
         <is>
           <t>入 力</t>
         </is>
       </c>
       <c r="AC39" s="5"/>
       <c r="AD39" s="6"/>
-      <c r="AE39" s="17" t="inlineStr">
+      <c r="AE39" s="27" t="inlineStr">
         <is>
           <t>校 合</t>
         </is>
@@ -1768,91 +1846,91 @@
     </row>
     <row r="40">
       <c r="B40" s="7"/>
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>は、□にレ印をつけてください。</t>
         </is>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="42" t="inlineStr">
         <is>
           <t>には、(注１)の押印及び(注２)の委任状は不要です。</t>
         </is>
       </c>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="13"/>
-      <c r="R40" s="14"/>
-      <c r="S40" s="14"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="13"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="13"/>
-      <c r="Z40" s="14"/>
-      <c r="AA40" s="15"/>
-      <c r="AB40" s="13"/>
-      <c r="AC40" s="14"/>
-      <c r="AD40" s="15"/>
-      <c r="AE40" s="13"/>
-      <c r="AF40" s="15"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="18"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="17"/>
+      <c r="X40" s="19"/>
+      <c r="Y40" s="17"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="17"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="19"/>
+      <c r="AE40" s="17"/>
+      <c r="AF40" s="19"/>
       <c r="AH40" s="9"/>
     </row>
     <row r="41">
-      <c r="B41" s="13"/>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="B41" s="17"/>
+      <c r="C41" s="28" t="inlineStr">
         <is>
           <t>（注２） 代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="43" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14"/>
-      <c r="S41" s="14"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="14"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="14"/>
-      <c r="AE41" s="14"/>
-      <c r="AF41" s="14"/>
-      <c r="AG41" s="14"/>
-      <c r="AH41" s="15"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
+      <c r="R41" s="18"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="18"/>
+      <c r="V41" s="18"/>
+      <c r="W41" s="18"/>
+      <c r="X41" s="18"/>
+      <c r="Y41" s="18"/>
+      <c r="Z41" s="18"/>
+      <c r="AA41" s="18"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="18"/>
+      <c r="AE41" s="18"/>
+      <c r="AF41" s="18"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="19"/>
     </row>
     <row r="42">
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>

--- a/data/out/test1/001328648_Python版_2pt.xlsx
+++ b/data/out/test1/001328648_Python版_2pt.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$AL$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet'!$A$1:$AM$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -166,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,85 +178,80 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -266,7 +261,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -635,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AK43"/>
+  <dimension ref="B2:AL43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.625" defaultRowHeight="18.25" customHeight="1"/>
   <sheetData>
     <row r="2">
@@ -675,6 +669,7 @@
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
       <c r="AK2" s="3"/>
+      <c r="AL2" s="4"/>
     </row>
     <row r="3">
       <c r="B3" s="4"/>
@@ -748,67 +743,70 @@
           <t>書</t>
         </is>
       </c>
-      <c r="AF3" s="3"/>
-      <c r="AK3" s="7"/>
+      <c r="AF3" s="7"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="4"/>
     </row>
     <row r="4">
       <c r="B4" s="4"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="10"/>
-      <c r="AK4" s="7"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="11"/>
+      <c r="AK4" s="8"/>
+      <c r="AL4" s="4"/>
     </row>
     <row r="5">
       <c r="B5" s="4"/>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>※</t>
         </is>
       </c>
-      <c r="D5" s="12"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
           <t>太枠の中に書いてください。</t>
         </is>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="14"/>
-      <c r="AK5" s="7"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
+      <c r="AK5" s="8"/>
+      <c r="AL5" s="4"/>
     </row>
     <row r="6">
       <c r="B6" s="4"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>（地方）法務局</t>
         </is>
@@ -816,13 +814,13 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="3"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="1"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="3"/>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>支局・出張所</t>
         </is>
@@ -832,10 +830,10 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
+      <c r="V6" s="1"/>
       <c r="W6" s="2"/>
       <c r="X6" s="2"/>
-      <c r="Y6" s="15" t="inlineStr">
+      <c r="Y6" s="14" t="inlineStr">
         <is>
           <t>年</t>
         </is>
@@ -843,19 +841,19 @@
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
       <c r="AB6" s="2"/>
-      <c r="AC6" s="15" t="inlineStr">
+      <c r="AC6" s="14" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
       <c r="AD6" s="2"/>
       <c r="AE6" s="2"/>
-      <c r="AF6" s="15" t="inlineStr">
+      <c r="AF6" s="14" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AG6" s="15" t="inlineStr">
+      <c r="AG6" s="14" t="inlineStr">
         <is>
           <t>届出</t>
         </is>
@@ -864,221 +862,239 @@
       <c r="AI6" s="2"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="7"/>
+      <c r="AL6" s="4"/>
     </row>
     <row r="7">
       <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="C7" s="1"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>印鑑の廃止届出</t>
         </is>
       </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="K7" s="9"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t>商号・名称</t>
         </is>
       </c>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
-      <c r="AJ7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="18"/>
       <c r="AK7" s="7"/>
+      <c r="AL7" s="4"/>
     </row>
     <row r="8">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>印鑑カードの</t>
         </is>
       </c>
-      <c r="J8" s="7"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="14"/>
-      <c r="AK8" s="14"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
+      <c r="AH8" s="10"/>
+      <c r="AI8" s="10"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="11"/>
+      <c r="AL8" s="4"/>
     </row>
     <row r="9">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>印鑑及び印鑑カー廃止届出</t>
         </is>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="20" t="inlineStr">
+      <c r="J9" s="20"/>
+      <c r="K9" s="21" t="inlineStr">
         <is>
           <t>本店・主たる事務所</t>
         </is>
       </c>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="9"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="9"/>
-      <c r="AE9" s="9"/>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="9"/>
-      <c r="AI9" s="9"/>
-      <c r="AJ9" s="10"/>
-      <c r="AK9" s="7"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="22"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="22"/>
+      <c r="AJ9" s="23"/>
+      <c r="AK9" s="20"/>
+      <c r="AL9" s="4"/>
     </row>
     <row r="10">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>ドの廃止届出</t>
         </is>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="J10" s="20"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>代表取締役・取締役・代表社員・代表理事・理事・支配人</t>
         </is>
       </c>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12"/>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12"/>
-      <c r="AJ10" s="14"/>
-      <c r="AK10" s="14"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
+      <c r="AH10" s="10"/>
+      <c r="AI10" s="10"/>
+      <c r="AJ10" s="18"/>
+      <c r="AK10" s="11"/>
+      <c r="AL10" s="4"/>
     </row>
     <row r="11">
       <c r="B11" s="4"/>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>(いずれかの□にレ印を</t>
         </is>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="J11" s="20"/>
+      <c r="K11" s="25" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="26" t="inlineStr">
         <is>
           <t>資格</t>
         </is>
       </c>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="18" t="inlineStr">
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t>(</t>
         </is>
       </c>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="9"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="18" t="inlineStr">
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="22"/>
+      <c r="AH11" s="22"/>
+      <c r="AI11" s="27" t="inlineStr">
         <is>
           <t>)</t>
         </is>
       </c>
-      <c r="AJ11" s="10"/>
-      <c r="AK11" s="7"/>
+      <c r="AJ11" s="23"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="4"/>
     </row>
     <row r="12">
       <c r="B12" s="4"/>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>つけてください。)</t>
         </is>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="J12" s="20"/>
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>鑑</t>
         </is>
@@ -1088,109 +1104,116 @@
           <t>氏名</t>
         </is>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="12"/>
-      <c r="W12" s="12"/>
-      <c r="X12" s="12"/>
-      <c r="Y12" s="12"/>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12"/>
-      <c r="AD12" s="12"/>
-      <c r="AE12" s="12"/>
-      <c r="AF12" s="12"/>
-      <c r="AG12" s="12"/>
-      <c r="AH12" s="12"/>
-      <c r="AI12" s="12"/>
-      <c r="AJ12" s="14"/>
-      <c r="AK12" s="14"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+      <c r="AB12" s="10"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="10"/>
+      <c r="AE12" s="10"/>
+      <c r="AF12" s="10"/>
+      <c r="AG12" s="10"/>
+      <c r="AH12" s="10"/>
+      <c r="AI12" s="10"/>
+      <c r="AJ12" s="18"/>
+      <c r="AK12" s="11"/>
+      <c r="AL12" s="4"/>
     </row>
     <row r="13">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="J13" s="20"/>
+      <c r="K13" s="28" t="inlineStr">
         <is>
           <t>提</t>
         </is>
       </c>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="9"/>
-      <c r="AE13" s="9"/>
-      <c r="AF13" s="9"/>
-      <c r="AG13" s="9"/>
-      <c r="AH13" s="9"/>
-      <c r="AI13" s="9"/>
-      <c r="AJ13" s="10"/>
-      <c r="AK13" s="7"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="23"/>
+      <c r="AK13" s="20"/>
+      <c r="AL13" s="4"/>
     </row>
     <row r="14">
       <c r="B14" s="4"/>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>（注１）</t>
         </is>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t>出</t>
         </is>
       </c>
-      <c r="L14" s="19"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="12"/>
-      <c r="W14" s="12"/>
-      <c r="X14" s="12"/>
-      <c r="Y14" s="12"/>
-      <c r="Z14" s="12"/>
-      <c r="AA14" s="12"/>
-      <c r="AB14" s="12"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="12"/>
-      <c r="AE14" s="12"/>
-      <c r="AF14" s="12"/>
-      <c r="AG14" s="12"/>
-      <c r="AH14" s="12"/>
-      <c r="AI14" s="12"/>
-      <c r="AJ14" s="14"/>
-      <c r="AK14" s="14"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+      <c r="AB14" s="10"/>
+      <c r="AC14" s="10"/>
+      <c r="AD14" s="10"/>
+      <c r="AE14" s="10"/>
+      <c r="AF14" s="10"/>
+      <c r="AG14" s="10"/>
+      <c r="AH14" s="10"/>
+      <c r="AI14" s="10"/>
+      <c r="AJ14" s="18"/>
+      <c r="AK14" s="11"/>
+      <c r="AL14" s="4"/>
     </row>
     <row r="15">
       <c r="B15" s="4"/>
@@ -1201,100 +1224,102 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="29" t="inlineStr">
+      <c r="J15" s="7"/>
+      <c r="K15" s="32" t="inlineStr">
         <is>
           <t>者</t>
         </is>
       </c>
-      <c r="L15" s="30" t="inlineStr">
+      <c r="L15" s="26" t="inlineStr">
         <is>
           <t>生年月日</t>
         </is>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="18" t="inlineStr">
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="27" t="inlineStr">
         <is>
           <t>大・昭・平・西暦</t>
         </is>
       </c>
-      <c r="R15" s="9"/>
-      <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="18" t="inlineStr">
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="27" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="18" t="inlineStr">
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="27" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="9"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="18" t="inlineStr">
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="22"/>
+      <c r="AH15" s="27" t="inlineStr">
         <is>
           <t>日生</t>
         </is>
       </c>
-      <c r="AI15" s="9"/>
-      <c r="AJ15" s="10"/>
-      <c r="AK15" s="7"/>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="23"/>
+      <c r="AK15" s="20"/>
+      <c r="AL15" s="4"/>
     </row>
     <row r="16">
       <c r="B16" s="4"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="31" t="inlineStr">
+      <c r="C16" s="33"/>
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>登印記鑑所のに提押出印し欄た</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="12"/>
-      <c r="W16" s="12"/>
-      <c r="X16" s="12"/>
-      <c r="Y16" s="12"/>
-      <c r="Z16" s="12"/>
-      <c r="AA16" s="12"/>
-      <c r="AB16" s="12"/>
-      <c r="AC16" s="12"/>
-      <c r="AD16" s="12"/>
-      <c r="AE16" s="12"/>
-      <c r="AF16" s="12"/>
-      <c r="AG16" s="12"/>
-      <c r="AH16" s="12"/>
-      <c r="AI16" s="12"/>
-      <c r="AJ16" s="14"/>
-      <c r="AK16" s="14"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
+      <c r="AA16" s="10"/>
+      <c r="AB16" s="10"/>
+      <c r="AC16" s="10"/>
+      <c r="AD16" s="10"/>
+      <c r="AE16" s="10"/>
+      <c r="AF16" s="10"/>
+      <c r="AG16" s="10"/>
+      <c r="AH16" s="10"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="18"/>
+      <c r="AK16" s="11"/>
+      <c r="AL16" s="4"/>
     </row>
     <row r="17">
       <c r="B17" s="4"/>
@@ -1305,65 +1330,68 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="22" t="inlineStr">
+      <c r="J17" s="7"/>
+      <c r="K17" s="24" t="inlineStr">
         <is>
           <t>印鑑カード番号</t>
         </is>
       </c>
-      <c r="AJ17" s="7"/>
-      <c r="AK17" s="7"/>
+      <c r="P17" s="4"/>
+      <c r="AJ17" s="8"/>
+      <c r="AK17" s="20"/>
+      <c r="AL17" s="4"/>
     </row>
     <row r="18">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="30" t="inlineStr">
+      <c r="J18" s="20"/>
+      <c r="K18" s="26" t="inlineStr">
         <is>
           <t>※カードのみを廃止する場合に、カード廃止の理由</t>
         </is>
       </c>
       <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
       <c r="P18" s="9"/>
-      <c r="Q18" s="9"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
       <c r="T18" s="9"/>
-      <c r="U18" s="32" t="inlineStr">
+      <c r="U18" s="12" t="inlineStr">
         <is>
           <t>亡失（なくなった）汚損（著しく汚れた)</t>
         </is>
       </c>
-      <c r="V18" s="9"/>
-      <c r="W18" s="9"/>
-      <c r="X18" s="9"/>
-      <c r="Y18" s="9"/>
-      <c r="Z18" s="9"/>
-      <c r="AA18" s="9"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
+      <c r="AA18" s="10"/>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
-      <c r="AD18" s="9"/>
-      <c r="AE18" s="32" t="inlineStr">
+      <c r="AD18" s="10"/>
+      <c r="AE18" s="12" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="AF18" s="9"/>
+      <c r="AF18" s="10"/>
       <c r="AG18" s="9"/>
-      <c r="AH18" s="9"/>
-      <c r="AI18" s="9"/>
-      <c r="AJ18" s="10"/>
+      <c r="AH18" s="10"/>
+      <c r="AI18" s="10"/>
+      <c r="AJ18" s="18"/>
       <c r="AK18" s="7"/>
+      <c r="AL18" s="4"/>
     </row>
     <row r="19">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="20"/>
       <c r="K19" s="1"/>
-      <c r="L19" s="33" t="inlineStr">
+      <c r="L19" s="35" t="inlineStr">
         <is>
           <t>□にレ印をつけてください。</t>
         </is>
@@ -1375,8 +1403,8 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="34" t="inlineStr">
+      <c r="T19" s="1"/>
+      <c r="U19" s="36" t="inlineStr">
         <is>
           <t>き損（破損した）</t>
         </is>
@@ -1387,94 +1415,97 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
       <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
+      <c r="AE19" s="1"/>
       <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
+      <c r="AG19" s="1"/>
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
       <c r="AJ19" s="3"/>
-      <c r="AK19" s="7"/>
+      <c r="AK19" s="20"/>
+      <c r="AL19" s="4"/>
     </row>
     <row r="20">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="30" t="inlineStr">
+      <c r="J20" s="20"/>
+      <c r="K20" s="26" t="inlineStr">
         <is>
           <t>申請人（注２）</t>
         </is>
       </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="9"/>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
       <c r="T20" s="9"/>
-      <c r="U20" s="18" t="inlineStr">
+      <c r="U20" s="26" t="inlineStr">
         <is>
           <t>印鑑提出者本人代理人</t>
         </is>
       </c>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
+      <c r="AA20" s="10"/>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
-      <c r="AD20" s="9"/>
-      <c r="AE20" s="9"/>
-      <c r="AF20" s="9"/>
-      <c r="AG20" s="9"/>
-      <c r="AH20" s="9"/>
-      <c r="AI20" s="9"/>
-      <c r="AJ20" s="10"/>
-      <c r="AK20" s="7"/>
+      <c r="AD20" s="10"/>
+      <c r="AE20" s="10"/>
+      <c r="AF20" s="10"/>
+      <c r="AG20" s="10"/>
+      <c r="AH20" s="10"/>
+      <c r="AI20" s="10"/>
+      <c r="AJ20" s="18"/>
+      <c r="AK20" s="11"/>
+      <c r="AL20" s="4"/>
     </row>
     <row r="21">
       <c r="B21" s="4"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="12"/>
-      <c r="Q21" s="12"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="12"/>
-      <c r="U21" s="12"/>
-      <c r="V21" s="12"/>
-      <c r="W21" s="12"/>
-      <c r="X21" s="12"/>
-      <c r="Y21" s="12"/>
-      <c r="Z21" s="12"/>
-      <c r="AA21" s="12"/>
-      <c r="AB21" s="12"/>
-      <c r="AC21" s="12"/>
-      <c r="AD21" s="12"/>
-      <c r="AE21" s="12"/>
-      <c r="AF21" s="12"/>
-      <c r="AG21" s="12"/>
-      <c r="AH21" s="12"/>
-      <c r="AI21" s="12"/>
-      <c r="AJ21" s="14"/>
-      <c r="AK21" s="14"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+      <c r="AB21" s="10"/>
+      <c r="AC21" s="10"/>
+      <c r="AD21" s="10"/>
+      <c r="AE21" s="10"/>
+      <c r="AF21" s="10"/>
+      <c r="AG21" s="10"/>
+      <c r="AH21" s="10"/>
+      <c r="AI21" s="10"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="11"/>
+      <c r="AL21" s="4"/>
     </row>
     <row r="22">
       <c r="B22" s="4"/>
@@ -1485,35 +1516,39 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="24" t="inlineStr">
+      <c r="J22" s="7"/>
+      <c r="K22" s="26" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="O22" s="8"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="W22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AA22" s="9"/>
-      <c r="AB22" s="9"/>
-      <c r="AC22" s="9"/>
-      <c r="AD22" s="9"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9"/>
-      <c r="AG22" s="9"/>
-      <c r="AH22" s="9"/>
-      <c r="AI22" s="9"/>
-      <c r="AJ22" s="10"/>
-      <c r="AK22" s="7"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22"/>
+      <c r="AG22" s="22"/>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="23"/>
+      <c r="AK22" s="20"/>
+      <c r="AL22" s="4"/>
     </row>
     <row r="23">
       <c r="B23" s="4"/>
@@ -1522,59 +1557,92 @@
           <t>（印鑑は鮮明に押</t>
         </is>
       </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="36" t="inlineStr">
+      <c r="K23" s="9"/>
+      <c r="L23" s="37" t="inlineStr">
         <is>
           <t>フリガナ</t>
         </is>
       </c>
-      <c r="M23" s="12"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="12"/>
-      <c r="Q23" s="12"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="12"/>
-      <c r="U23" s="12"/>
-      <c r="V23" s="12"/>
-      <c r="W23" s="12"/>
-      <c r="X23" s="12"/>
-      <c r="Y23" s="12"/>
-      <c r="Z23" s="12"/>
-      <c r="AA23" s="12"/>
-      <c r="AB23" s="12"/>
-      <c r="AC23" s="12"/>
-      <c r="AD23" s="12"/>
-      <c r="AE23" s="12"/>
-      <c r="AF23" s="12"/>
-      <c r="AG23" s="12"/>
-      <c r="AH23" s="12"/>
-      <c r="AI23" s="12"/>
-      <c r="AJ23" s="14"/>
-      <c r="AK23" s="14"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+      <c r="AB23" s="10"/>
+      <c r="AC23" s="10"/>
+      <c r="AD23" s="10"/>
+      <c r="AE23" s="10"/>
+      <c r="AF23" s="10"/>
+      <c r="AG23" s="10"/>
+      <c r="AH23" s="10"/>
+      <c r="AI23" s="10"/>
+      <c r="AJ23" s="18"/>
+      <c r="AK23" s="11"/>
+      <c r="AL23" s="4"/>
     </row>
     <row r="24">
       <c r="B24" s="4"/>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>印してください。）</t>
         </is>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="24" t="inlineStr">
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="38" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="AK24" s="21"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22"/>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="22"/>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="23"/>
+      <c r="AK24" s="11"/>
+      <c r="AL24" s="4"/>
     </row>
     <row r="25">
       <c r="B25" s="4"/>
@@ -1585,12 +1653,12 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" s="1"/>
       <c r="P25" s="2"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
@@ -1612,33 +1680,65 @@
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
       <c r="AJ25" s="3"/>
-      <c r="AK25" s="38"/>
+      <c r="AK25" s="7"/>
+      <c r="AL25" s="4"/>
     </row>
     <row r="26">
       <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="Q26" s="17" t="inlineStr">
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="36" t="inlineStr">
         <is>
           <t>委</t>
         </is>
       </c>
-      <c r="U26" s="17" t="inlineStr">
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="16" t="inlineStr">
         <is>
           <t>任</t>
         </is>
       </c>
-      <c r="X26" s="17" t="inlineStr">
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="16" t="inlineStr">
         <is>
           <t>状</t>
         </is>
       </c>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
       <c r="AJ26" s="7"/>
-      <c r="AK26" s="39"/>
+      <c r="AK26" s="7"/>
+      <c r="AL26" s="4"/>
     </row>
     <row r="27">
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
-      <c r="E27" s="40" t="inlineStr">
+      <c r="D27" s="4"/>
+      <c r="E27" s="39" t="inlineStr">
         <is>
           <t>私は、（住所）</t>
         </is>
@@ -1648,288 +1748,363 @@
           <t>私は、（住所）</t>
         </is>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="14"/>
-      <c r="AJ27" s="7"/>
-      <c r="AK27" s="39"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="1"/>
+      <c r="AJ27" s="20"/>
+      <c r="AK27" s="20"/>
+      <c r="AL27" s="4"/>
     </row>
     <row r="28">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="D28" s="4"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>（氏名）</t>
         </is>
       </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="14"/>
-      <c r="AJ28" s="7"/>
-      <c r="AK28" s="39"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="1"/>
+      <c r="AJ28" s="20"/>
+      <c r="AK28" s="20"/>
+      <c r="AL28" s="4"/>
     </row>
     <row r="29">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="D29" s="4"/>
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>を代理人と定め、印鑑の廃止届出、印鑑カードの廃止届出、印鑑及び印鑑カード</t>
         </is>
       </c>
-      <c r="AJ29" s="7"/>
-      <c r="AK29" s="39"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="1"/>
+      <c r="AJ29" s="20"/>
+      <c r="AK29" s="20"/>
+      <c r="AL29" s="4"/>
     </row>
     <row r="30">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="D30" s="4"/>
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>の廃止届出、添付書面の原本還付請求及び受領の権限を委任します。</t>
         </is>
       </c>
-      <c r="AJ30" s="7"/>
-      <c r="AK30" s="39"/>
+      <c r="AJ30" s="20"/>
+      <c r="AK30" s="20"/>
+      <c r="AL30" s="4"/>
     </row>
     <row r="31">
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="J31" s="17" t="inlineStr">
+      <c r="D31" s="4"/>
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>年</t>
         </is>
       </c>
-      <c r="L31" s="17" t="inlineStr">
+      <c r="L31" s="19" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="O31" s="17" t="inlineStr">
+      <c r="O31" s="19" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="AJ31" s="7"/>
-      <c r="AK31" s="39"/>
+      <c r="AJ31" s="20"/>
+      <c r="AK31" s="20"/>
+      <c r="AL31" s="4"/>
     </row>
     <row r="32">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="D32" s="4"/>
+      <c r="F32" s="36" t="inlineStr">
         <is>
           <t>住所</t>
         </is>
       </c>
-      <c r="AJ32" s="7"/>
-      <c r="AK32" s="39"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="AJ32" s="20"/>
+      <c r="AK32" s="20"/>
+      <c r="AL32" s="4"/>
     </row>
     <row r="33">
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="D33" s="4"/>
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="AA33" s="17" t="inlineStr">
+      <c r="AA33" s="36" t="inlineStr">
         <is>
           <t>印</t>
         </is>
       </c>
-      <c r="AD33" s="41" t="inlineStr">
+      <c r="AB33" s="1"/>
+      <c r="AD33" s="40" t="inlineStr">
         <is>
           <t>登記所に提</t>
         </is>
       </c>
-      <c r="AJ33" s="7"/>
-      <c r="AK33" s="39"/>
+      <c r="AJ33" s="20"/>
+      <c r="AK33" s="20"/>
+      <c r="AL33" s="4"/>
     </row>
     <row r="34">
       <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="E34" s="17" t="inlineStr">
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>市区町村長作成の印鑑証明書は、登記申請書に添付のものを援用する。（注１）</t>
         </is>
       </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
       <c r="AJ34" s="7"/>
-      <c r="AK34" s="39"/>
+      <c r="AK34" s="7"/>
+      <c r="AL34" s="4"/>
     </row>
     <row r="35">
       <c r="B35" s="4"/>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>（注１）の印鑑を押印し、作成後３か月以内の市区町村長の証明した印鑑証明書を添付してください。登記所に提出した印鑑を押印してください。この押印ができない場合は、市区町村に登録済み登</t>
         </is>
       </c>
-      <c r="AJ35" s="7"/>
-      <c r="AK35" s="39"/>
+      <c r="AJ35" s="8"/>
+      <c r="AK35" s="20"/>
+      <c r="AL35" s="4"/>
     </row>
     <row r="36">
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="F36" s="41" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>記申請書に添付した印鑑証明書を援用する場合（登記の申請と同時に印鑑を届け出た場合に限る。）</t>
         </is>
       </c>
-      <c r="AJ36" s="7"/>
-      <c r="AK36" s="39"/>
+      <c r="AJ36" s="8"/>
+      <c r="AK36" s="20"/>
+      <c r="AL36" s="4"/>
     </row>
     <row r="37">
       <c r="B37" s="4"/>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>（注２）は、□にレ印をつけてください。代理人が届け出るときは、代理人の住所・氏名を記載してください。この場合、委任状に所要</t>
         </is>
       </c>
-      <c r="AJ37" s="7"/>
-      <c r="AK37" s="39"/>
+      <c r="AJ37" s="8"/>
+      <c r="AK37" s="20"/>
+      <c r="AL37" s="4"/>
     </row>
     <row r="38">
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
-      <c r="F38" s="41" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>事項を記載し（該当する□にはレ印をつける）、登記所に提出した印鑑を押印してください。</t>
         </is>
       </c>
-      <c r="AJ38" s="7"/>
-      <c r="AK38" s="39"/>
+      <c r="AJ38" s="8"/>
+      <c r="AK38" s="20"/>
+      <c r="AL38" s="4"/>
     </row>
     <row r="39">
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="F39" s="41" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>村長の証明した印鑑証明書を添付してください。この押印ができない場合は、市区町村に登録済みの印鑑を押印し、作成後３か月以内の市区町</t>
         </is>
       </c>
-      <c r="AJ39" s="7"/>
-      <c r="AK39" s="39"/>
+      <c r="AJ39" s="8"/>
+      <c r="AK39" s="20"/>
+      <c r="AL39" s="4"/>
     </row>
     <row r="40">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="41" t="inlineStr">
+      <c r="D40" s="40" t="inlineStr">
         <is>
           <t>（注３）印鑑カードの交付を受けている場印鑑処理番号受付調査入力校合</t>
         </is>
       </c>
-      <c r="R40" s="21"/>
-      <c r="S40" s="40" t="inlineStr">
+      <c r="R40" s="11"/>
+      <c r="S40" s="39" t="inlineStr">
         <is>
           <t>印鑑処理番号</t>
         </is>
       </c>
-      <c r="T40" s="12"/>
-      <c r="U40" s="12"/>
-      <c r="V40" s="12"/>
-      <c r="W40" s="14"/>
-      <c r="X40" s="21"/>
-      <c r="Y40" s="40" t="inlineStr">
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="11"/>
+      <c r="Y40" s="39" t="inlineStr">
         <is>
           <t>受 付</t>
         </is>
       </c>
-      <c r="Z40" s="12"/>
-      <c r="AA40" s="14"/>
-      <c r="AB40" s="40" t="inlineStr">
+      <c r="Z40" s="10"/>
+      <c r="AA40" s="11"/>
+      <c r="AB40" s="39" t="inlineStr">
         <is>
           <t>調 査</t>
         </is>
       </c>
-      <c r="AC40" s="12"/>
-      <c r="AD40" s="14"/>
-      <c r="AE40" s="40" t="inlineStr">
+      <c r="AC40" s="10"/>
+      <c r="AD40" s="11"/>
+      <c r="AE40" s="39" t="inlineStr">
         <is>
           <t>入 力</t>
         </is>
       </c>
-      <c r="AF40" s="12"/>
-      <c r="AG40" s="14"/>
-      <c r="AH40" s="40" t="inlineStr">
+      <c r="AF40" s="10"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="39" t="inlineStr">
         <is>
           <t>校 合</t>
         </is>
       </c>
-      <c r="AI40" s="12"/>
-      <c r="AJ40" s="14"/>
-      <c r="AK40" s="21"/>
+      <c r="AI40" s="10"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="11"/>
+      <c r="AL40" s="4"/>
     </row>
     <row r="41">
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="F41" s="41" t="inlineStr">
+      <c r="F41" s="40" t="inlineStr">
         <is>
           <t>合は、返納してください。この場合には、(注１)の押印及び(注２)の委</t>
         </is>
       </c>
-      <c r="R41" s="1"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="2"/>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="2"/>
-      <c r="AD41" s="3"/>
-      <c r="AE41" s="1"/>
-      <c r="AF41" s="2"/>
-      <c r="AG41" s="3"/>
-      <c r="AH41" s="1"/>
-      <c r="AI41" s="2"/>
-      <c r="AJ41" s="3"/>
-      <c r="AK41" s="39"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="10"/>
+      <c r="AA41" s="11"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="10"/>
+      <c r="AD41" s="11"/>
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="10"/>
+      <c r="AG41" s="18"/>
+      <c r="AH41" s="9"/>
+      <c r="AI41" s="10"/>
+      <c r="AJ41" s="18"/>
+      <c r="AK41" s="11"/>
+      <c r="AL41" s="4"/>
     </row>
     <row r="42">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="42" t="inlineStr">
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="41" t="inlineStr">
         <is>
           <t>任状は不要です。</t>
         </is>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="9"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="10"/>
-      <c r="Y42" s="8"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="10"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="10"/>
-      <c r="AE42" s="8"/>
-      <c r="AF42" s="9"/>
-      <c r="AG42" s="10"/>
-      <c r="AH42" s="8"/>
-      <c r="AI42" s="9"/>
-      <c r="AJ42" s="10"/>
-      <c r="AK42" s="43"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="22"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="22"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="22"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="22"/>
+      <c r="X42" s="30"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="22"/>
+      <c r="AA42" s="23"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="22"/>
+      <c r="AD42" s="23"/>
+      <c r="AE42" s="33"/>
+      <c r="AF42" s="22"/>
+      <c r="AG42" s="23"/>
+      <c r="AH42" s="33"/>
+      <c r="AI42" s="22"/>
+      <c r="AJ42" s="23"/>
+      <c r="AK42" s="30"/>
+      <c r="AL42" s="4"/>
     </row>
     <row r="43">
-      <c r="C43" s="44" t="inlineStr">
+      <c r="B43" s="2"/>
+      <c r="C43" s="42" t="inlineStr">
         <is>
           <t>（乙号・10)</t>
         </is>

--- a/data/out/test1/001328648_Python版_2pt.xlsx
+++ b/data/out/test1/001328648_Python版_2pt.xlsx
@@ -28,31 +28,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="19.6"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="10.9"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="9.800000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="8.800000000000001"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6.5"/>
     </font>
     <font>
-      <name val="MS Gothic"/>
+      <name val="MS 明朝"/>
       <sz val="6"/>
     </font>
   </fonts>
@@ -172,28 +172,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -203,60 +203,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -624,42 +624,42 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:AH46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="2.74" defaultRowHeight="18.25" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="2.65" defaultRowHeight="18.25" customHeight="1"/>
   <cols>
-    <col width="2.74" customWidth="1" min="1" max="1"/>
-    <col width="2.74" customWidth="1" min="2" max="2"/>
-    <col width="2.74" customWidth="1" min="3" max="3"/>
-    <col width="2.74" customWidth="1" min="4" max="4"/>
-    <col width="2.74" customWidth="1" min="5" max="5"/>
-    <col width="2.74" customWidth="1" min="6" max="6"/>
-    <col width="2.74" customWidth="1" min="7" max="7"/>
-    <col width="2.74" customWidth="1" min="8" max="8"/>
-    <col width="2.74" customWidth="1" min="9" max="9"/>
-    <col width="2.74" customWidth="1" min="10" max="10"/>
-    <col width="2.74" customWidth="1" min="11" max="11"/>
-    <col width="2.74" customWidth="1" min="12" max="12"/>
-    <col width="2.74" customWidth="1" min="13" max="13"/>
-    <col width="2.74" customWidth="1" min="14" max="14"/>
-    <col width="2.74" customWidth="1" min="15" max="15"/>
-    <col width="2.74" customWidth="1" min="16" max="16"/>
-    <col width="2.74" customWidth="1" min="17" max="17"/>
-    <col width="2.74" customWidth="1" min="18" max="18"/>
-    <col width="2.74" customWidth="1" min="19" max="19"/>
-    <col width="2.74" customWidth="1" min="20" max="20"/>
-    <col width="2.74" customWidth="1" min="21" max="21"/>
-    <col width="2.74" customWidth="1" min="22" max="22"/>
-    <col width="2.74" customWidth="1" min="23" max="23"/>
-    <col width="2.74" customWidth="1" min="24" max="24"/>
-    <col width="2.74" customWidth="1" min="25" max="25"/>
-    <col width="2.74" customWidth="1" min="26" max="26"/>
-    <col width="2.74" customWidth="1" min="27" max="27"/>
-    <col width="2.74" customWidth="1" min="28" max="28"/>
-    <col width="2.74" customWidth="1" min="29" max="29"/>
-    <col width="2.74" customWidth="1" min="30" max="30"/>
-    <col width="2.74" customWidth="1" min="31" max="31"/>
-    <col width="2.74" customWidth="1" min="32" max="32"/>
-    <col width="2.74" customWidth="1" min="33" max="33"/>
-    <col width="2.74" customWidth="1" min="34" max="34"/>
+    <col width="2.65" customWidth="1" min="1" max="1"/>
+    <col width="2.65" customWidth="1" min="2" max="2"/>
+    <col width="2.65" customWidth="1" min="3" max="3"/>
+    <col width="2.65" customWidth="1" min="4" max="4"/>
+    <col width="2.65" customWidth="1" min="5" max="5"/>
+    <col width="2.65" customWidth="1" min="6" max="6"/>
+    <col width="2.65" customWidth="1" min="7" max="7"/>
+    <col width="2.65" customWidth="1" min="8" max="8"/>
+    <col width="2.65" customWidth="1" min="9" max="9"/>
+    <col width="2.65" customWidth="1" min="10" max="10"/>
+    <col width="2.65" customWidth="1" min="11" max="11"/>
+    <col width="2.65" customWidth="1" min="12" max="12"/>
+    <col width="2.65" customWidth="1" min="13" max="13"/>
+    <col width="2.65" customWidth="1" min="14" max="14"/>
+    <col width="2.65" customWidth="1" min="15" max="15"/>
+    <col width="2.65" customWidth="1" min="16" max="16"/>
+    <col width="2.65" customWidth="1" min="17" max="17"/>
+    <col width="2.65" customWidth="1" min="18" max="18"/>
+    <col width="2.65" customWidth="1" min="19" max="19"/>
+    <col width="2.65" customWidth="1" min="20" max="20"/>
+    <col width="2.65" customWidth="1" min="21" max="21"/>
+    <col width="2.65" customWidth="1" min="22" max="22"/>
+    <col width="2.65" customWidth="1" min="23" max="23"/>
+    <col width="2.65" customWidth="1" min="24" max="24"/>
+    <col width="2.65" customWidth="1" min="25" max="25"/>
+    <col width="2.65" customWidth="1" min="26" max="26"/>
+    <col width="2.65" customWidth="1" min="27" max="27"/>
+    <col width="2.65" customWidth="1" min="28" max="28"/>
+    <col width="2.65" customWidth="1" min="29" max="29"/>
+    <col width="2.65" customWidth="1" min="30" max="30"/>
+    <col width="2.65" customWidth="1" min="31" max="31"/>
+    <col width="2.65" customWidth="1" min="32" max="32"/>
+    <col width="2.65" customWidth="1" min="33" max="33"/>
+    <col width="2.65" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="2">
